--- a/data/trans_dic/P3A$otraNOcobra-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,81</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,7</t>
+          <t>0,03; 1,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,28</t>
+          <t>0,14; 1,31</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,24</t>
+          <t>0,2; 1,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,83</t>
+          <t>0,2; 0,89</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,54</t>
+          <t>0,45; 2,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,05</t>
+          <t>0,18; 1,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,53</t>
+          <t>0,47; 1,55</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,67</t>
+          <t>0,78; 2,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,32</t>
+          <t>1,35; 3,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,6</t>
+          <t>1,2; 2,6</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,47</t>
+          <t>2,34; 5,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,94</t>
+          <t>1,7; 7,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,53</t>
+          <t>1,97; 5,55</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,45; 26,02</t>
+          <t>17,94; 25,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,62; 26,29</t>
+          <t>20,6; 26,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,48; 24,97</t>
+          <t>20,45; 24,91</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,77</t>
+          <t>2,29; 3,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,47</t>
+          <t>3,16; 4,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,98</t>
+          <t>2,92; 3,95</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 27254</t>
+          <t>0; 30972</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7008</t>
+          <t>0; 6941</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 26822</t>
+          <t>0; 34107</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11356</t>
+          <t>0; 9583</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173; 8705</t>
+          <t>148; 7601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1211; 11996</t>
+          <t>1309; 12243</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5218</t>
+          <t>0; 5690</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1168; 7336</t>
+          <t>1205; 8095</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1975; 9386</t>
+          <t>2293; 10028</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3666; 22561</t>
+          <t>4014; 21967</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1244; 7489</t>
+          <t>1270; 7327</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7179; 24511</t>
+          <t>7464; 24747</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4361; 14982</t>
+          <t>4405; 16135</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7470; 18178</t>
+          <t>7397; 17675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13798; 28867</t>
+          <t>13263; 28820</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8514; 20063</t>
+          <t>8607; 20955</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9796; 42187</t>
+          <t>10317; 42788</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20385; 53926</t>
+          <t>19182; 54068</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>52181; 73560</t>
+          <t>50720; 72747</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>87801; 111945</t>
+          <t>87711; 111177</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>145090; 176944</t>
+          <t>144921; 176493</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>80790; 130554</t>
+          <t>79067; 129235</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>118675; 165885</t>
+          <t>117353; 167125</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>219839; 285265</t>
+          <t>209298; 283026</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraNOcobra-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,48</t>
+          <t>0,19; 1,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,31</t>
+          <t>0,21; 1,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,37</t>
+          <t>0,19; 1,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,89</t>
+          <t>0,19; 0,92</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,47</t>
+          <t>0,89; 2,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,03</t>
+          <t>0,17; 1,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,55</t>
+          <t>0,64; 1,73</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,87</t>
+          <t>0,73; 2,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,23</t>
+          <t>1,28; 3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,6</t>
+          <t>1,21; 2,47</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,71</t>
+          <t>2,36; 5,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,04</t>
+          <t>4,65; 8,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,55</t>
+          <t>3,8; 6,11</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,94; 25,73</t>
+          <t>17,11; 24,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,6; 26,11</t>
+          <t>20,2; 25,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,45; 24,91</t>
+          <t>20,03; 24,4</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,74</t>
+          <t>2,52; 3,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,5</t>
+          <t>3,75; 4,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,95</t>
+          <t>3,33; 4,03</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>4292</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 30972</t>
+          <t>0; 16442</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6941</t>
+          <t>0; 6228</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 34107</t>
+          <t>0; 16129</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>6080</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9583</t>
+          <t>0; 9279</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148; 7601</t>
+          <t>929; 8845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1309; 12243</t>
+          <t>2066; 13723</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5200</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5690</t>
+          <t>0; 5830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1205; 8095</t>
+          <t>1160; 7262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2293; 10028</t>
+          <t>2345; 11435</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>15281</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4014; 21967</t>
+          <t>6255; 20525</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1270; 7327</t>
+          <t>1269; 8331</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7464; 24747</t>
+          <t>9226; 24907</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>21407</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4405; 16135</t>
+          <t>4438; 15607</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7397; 17675</t>
+          <t>7807; 18452</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13263; 28820</t>
+          <t>14762; 30097</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39217</t>
+          <t>41743</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8607; 20955</t>
+          <t>9574; 22265</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10317; 42788</t>
+          <t>20399; 35129</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19182; 54068</t>
+          <t>32118; 51599</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>61379</t>
+          <t>64691</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>99397</t>
+          <t>106693</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>160776</t>
+          <t>171384</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50720; 72747</t>
+          <t>53061; 76864</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>87711; 111177</t>
+          <t>93849; 119888</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>144921; 176493</t>
+          <t>155221; 189066</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>146841</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>251965</t>
+          <t>265387</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>79067; 129235</t>
+          <t>88936; 127027</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>117353; 167125</t>
+          <t>140113; 177963</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>209298; 283026</t>
+          <t>241658; 293041</t>
         </is>
       </c>
     </row>
